--- a/data_raw/individual_deposit.xlsx
+++ b/data_raw/individual_deposit.xlsx
@@ -1,216 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>住户存款余额(亿元)</t>
-  </si>
-  <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>乌鲁木齐</t>
-  </si>
-  <si>
-    <t>兰州</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
-    <t>南京</t>
-  </si>
-  <si>
-    <t>南宁</t>
-  </si>
-  <si>
-    <t>南昌</t>
-  </si>
-  <si>
-    <t>厦门</t>
-  </si>
-  <si>
-    <t>合肥</t>
-  </si>
-  <si>
-    <t>呼和浩特</t>
-  </si>
-  <si>
-    <t>哈尔滨</t>
-  </si>
-  <si>
-    <t>大连</t>
-  </si>
-  <si>
-    <t>天津</t>
-  </si>
-  <si>
-    <t>太原</t>
-  </si>
-  <si>
-    <t>宁波</t>
-  </si>
-  <si>
-    <t>广州</t>
-  </si>
-  <si>
-    <t>成都</t>
-  </si>
-  <si>
-    <t>拉萨</t>
-  </si>
-  <si>
-    <t>昆明</t>
-  </si>
-  <si>
-    <t>杭州</t>
-  </si>
-  <si>
-    <t>武汉</t>
-  </si>
-  <si>
-    <t>沈阳</t>
-  </si>
-  <si>
-    <t>济南</t>
-  </si>
-  <si>
-    <t>海口</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>石家庄</t>
-  </si>
-  <si>
-    <t>福州</t>
-  </si>
-  <si>
-    <t>西宁</t>
-  </si>
-  <si>
-    <t>西安</t>
-  </si>
-  <si>
-    <t>贵阳</t>
-  </si>
-  <si>
-    <t>郑州</t>
-  </si>
-  <si>
-    <t>重庆</t>
-  </si>
-  <si>
-    <t>银川</t>
-  </si>
-  <si>
-    <t>长春</t>
-  </si>
-  <si>
-    <t>长沙</t>
-  </si>
-  <si>
-    <t>青岛</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -225,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -541,2293 +420,2452 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>住户存款余额(亿元)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>8730</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>8745.219999999999</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>11464.15</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>13707.32</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>15650.2391213502</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>17288.4547267085</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>19506.7</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>20486.2536071674</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>21269.3</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>23384.7295</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>23639.8015</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>24338.48</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>27071.74</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>31727.73</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>36733.9728</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>41150.4</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>52638</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>58319.9286</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>63910.9863</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>678.16</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>679.53</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>872.22</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>1040.707</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>1242.8526</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>1470.3412</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>1715.9659</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>1896.3048</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>1974.84</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>2157.3093</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>2295.6888</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>2600.3858</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>2871.1134</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>3171.7101</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>3680.2754</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>4027.8586</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>4647.5182</v>
       </c>
-      <c r="S3">
+      <c r="S3" t="n">
         <v>5305.9981</v>
       </c>
-      <c r="T3">
+      <c r="T3" t="n">
         <v>5905.76</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4">
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>687.7518</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>649.6569</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>823.83</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>1089.9721</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>1295.9451</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>1480.1626</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>1743.1811</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>2021.5573</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>2262.9407</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>2608.5399</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>2796.2448</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>2949.2658</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>3244.0812</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>3571.176</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>3859.627</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>4082.9699</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>4569.2581</v>
       </c>
-      <c r="S4">
+      <c r="S4" t="n">
         <v>5130.1717</v>
       </c>
-      <c r="T4">
+      <c r="T4" t="n">
         <v>5639.5427</v>
       </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5">
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>8705.6</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>9155.34</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>11952.84</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>14672.1</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>17003.1121859824</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>19126.1369907331</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>21644.9</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>23086.4149916846</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>24158.4</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>23913.967</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>28012.0329</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>28962.2</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>34018.9631</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>37309.675</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>42888.765</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>47184.3121</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>56915.7573</v>
       </c>
-      <c r="S5">
+      <c r="S5" t="n">
         <v>64020.3563</v>
       </c>
-      <c r="T5">
+      <c r="T5" t="n">
         <v>70398.14599999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>1834.88</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>1951.1599</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>2505.3308</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>3056.3486</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>3511.85</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>3910.2037</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>4465.37</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>4883.29</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>5055.7718</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>5535.5266</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>5894.468</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>6019.7012</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>6914.8437</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>8299.639999999999</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>9499.2456</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>10636.7754</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>13078.0479</v>
       </c>
-      <c r="S6">
+      <c r="S6" t="n">
         <v>15228.9498</v>
       </c>
-      <c r="T6">
+      <c r="T6" t="n">
         <v>17091.8481</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>681.4521999999999</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>714.7919000000001</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>88.6542</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>1116.1975</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>1375.8853</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>1581.0297</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>1863.8024</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>2321.1576</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>2529.8556</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>2700.3678</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>2924.5457</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>3176.6881</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>3542.8272</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>3960.3083</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>4415.3458</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>4878.7971</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>5521.8223</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>6117.1299</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>6713.2205</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>733.8474</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>744.5682</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>955.4016</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>1181.8238</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>1417.5807</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>1603.9632</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>1853.5679</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>2051.1635</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>2149.3277</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>2491.3925</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>2722.4199</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>2869.8392</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>3132.045</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>3618.0632</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>4278.6505</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>4737.9847</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>5750.3712</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>6641.7365</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>7516.1403</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>680.8196</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>739.998</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>929.4447</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>1158.0996</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>1384.666</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>1558.7417</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>1680.1926</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>1950.1009</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>1972.0201</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>2050.2746</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>2172.0007</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>2292.056</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>2610.177</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>3062</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>3684.3858</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>4197.7867</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>5213.3921</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>5963.1828</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>6546.1784</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>624.5599999999999</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>673.0856</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>852.8294</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>1031.8141</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>1233.7343</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1689.5435</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>2065.5745</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>2355.7723</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>2539.4998</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>3018.5366</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>3281.2636</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>3489.1815</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>4003.407</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>4667.2164</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>5589.4046</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>6394.1404</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>7958.0409</v>
       </c>
-      <c r="S10">
+      <c r="S10" t="n">
         <v>9387.1358</v>
       </c>
-      <c r="T10">
+      <c r="T10" t="n">
         <v>10785.8387</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11">
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>453.0845</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>511.3839</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>640.5628</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>775.8896</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>929.8099999999999</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>1053.68</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>1243.2682</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>1414.6189</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>1480.8828</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>1683.9561</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>1866.0141</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>1953.4119</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>2174.0867</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>2391.6363</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>2623.7502</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>2893.0958</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>3372.4633</v>
       </c>
-      <c r="S11">
+      <c r="S11" t="n">
         <v>3903.7037</v>
       </c>
-      <c r="T11">
+      <c r="T11" t="n">
         <v>3771.4489</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12">
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>1563.8334</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>1541.1019</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>1916.7579</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>2249.5467</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>2580.1409</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>2896.5659</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>3320.6732</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>3593.5628</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>3768.8193</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>4370.4197</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>4671.897</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>4938.373</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>5394.256</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>6291.8401</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>7311.3923</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>8187.2016</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>9645.654</v>
       </c>
-      <c r="S12">
+      <c r="S12" t="n">
         <v>11005.5949</v>
       </c>
-      <c r="T12">
+      <c r="T12" t="n">
         <v>12056.2573</v>
       </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>1866.4886</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>1836.9933</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>2388.9658</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>2930.6487</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>3374.8155</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>3672.2094</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>4160.468</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>4483.7717</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>4666.7061</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>5107.8913</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>5277.6562</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>5414.4951</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>6039.9697</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>6842.2887</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>7843.7553</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>8686.066699999999</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>10070.2174</v>
       </c>
-      <c r="S13">
+      <c r="S13" t="n">
         <v>11390.7291</v>
       </c>
-      <c r="T13">
+      <c r="T13" t="n">
         <v>12401.4925</v>
       </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14">
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>2808.1</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>3083.07</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>3978.04</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>4885.86</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>5558.2339041591</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>6123.0772715164</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>7055.4</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>7612.3069626508</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>7916.9</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>8743.7889</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>9125.3832</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>9558.0478</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="n">
         <v>10746.1653</v>
       </c>
-      <c r="O14">
+      <c r="O14" t="n">
         <v>12639.6371</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="n">
         <v>14865.7121</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" t="n">
         <v>16244.1217</v>
       </c>
-      <c r="R14">
+      <c r="R14" t="n">
         <v>19211.245</v>
       </c>
-      <c r="S14">
+      <c r="S14" t="n">
         <v>21996.8247</v>
       </c>
-      <c r="T14">
+      <c r="T14" t="n">
         <v>24069.6285</v>
       </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15">
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>1183.9536</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>1307.2386</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>1728.9231</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>2085.0017</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>2386.7861</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>2775.5685</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>3021.4991</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>3307.9851</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>3325.7782</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>3432.12</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>3661.76</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>4384.88</v>
       </c>
-      <c r="N15">
+      <c r="N15" t="n">
         <v>4767.46</v>
       </c>
-      <c r="O15">
+      <c r="O15" t="n">
         <v>5252.08</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="n">
         <v>5896.93</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" t="n">
         <v>6566.4</v>
       </c>
-      <c r="R15">
+      <c r="R15" t="n">
         <v>7761.93</v>
       </c>
-      <c r="S15">
+      <c r="S15" t="n">
         <v>8825.188</v>
       </c>
-      <c r="T15">
+      <c r="T15" t="n">
         <v>9741.197399999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>1752.0388</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>1856.0788</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>2365.1493</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>2901.7634</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>3312.1737</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>3696.2819</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>4175.9634</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>4562.3634</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>4780.3126</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>5302.8406</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>5689.4416</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>5902.6776</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="n">
         <v>6561.2648</v>
       </c>
-      <c r="O16">
+      <c r="O16" t="n">
         <v>7475.4684</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="n">
         <v>8522.0707</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" t="n">
         <v>9387.3063</v>
       </c>
-      <c r="R16">
+      <c r="R16" t="n">
         <v>11749.7481</v>
       </c>
-      <c r="S16">
+      <c r="S16" t="n">
         <v>14282.0093</v>
       </c>
-      <c r="T16">
+      <c r="T16" t="n">
         <v>16255.5179</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>5562.3554</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>5855.79</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>7111.27</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>8214.209999999999</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>9302.33</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>10032.62</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>11310.69</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>12496.6918</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>12825.6427</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>13602.3823</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>13995.7861</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>14625.6284</v>
       </c>
-      <c r="N17">
+      <c r="N17" t="n">
         <v>16042.0619</v>
       </c>
-      <c r="O17">
+      <c r="O17" t="n">
         <v>17980.5558</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="n">
         <v>20774.1257</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" t="n">
         <v>22768.5313</v>
       </c>
-      <c r="R17">
+      <c r="R17" t="n">
         <v>26479.869</v>
       </c>
-      <c r="S17">
+      <c r="S17" t="n">
         <v>29714.9503</v>
       </c>
-      <c r="T17">
+      <c r="T17" t="n">
         <v>32394.0385</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18">
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>2411.4509</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>2466.3956</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>3264.7872</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>4233.7109</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>5071.372</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>5944.7689</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>7060.0314</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>8151.589</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>8976.9401</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>9922.1841</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>10808</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>11970.8368</v>
       </c>
-      <c r="N18">
+      <c r="N18" t="n">
         <v>13141.4672</v>
       </c>
-      <c r="O18">
+      <c r="O18" t="n">
         <v>14900.5522</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="n">
         <v>17084.9889</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" t="n">
         <v>19020.4642</v>
       </c>
-      <c r="R18">
+      <c r="R18" t="n">
         <v>22402.7781</v>
       </c>
-      <c r="S18">
+      <c r="S18" t="n">
         <v>25768.9379</v>
       </c>
-      <c r="T18">
+      <c r="T18" t="n">
         <v>28991.8879</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19">
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
         <v>90.47</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>104.45</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>127.3</v>
       </c>
-      <c r="G19">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
         <v>178.2976</v>
       </c>
-      <c r="J19">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
         <v>559.2769</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="n">
         <v>341.1873</v>
       </c>
-      <c r="L19">
+      <c r="L19" t="n">
         <v>408.87</v>
       </c>
-      <c r="M19">
+      <c r="M19" t="n">
         <v>442.6917</v>
       </c>
-      <c r="N19">
+      <c r="N19" t="n">
         <v>461.4153</v>
       </c>
-      <c r="O19">
+      <c r="O19" t="n">
         <v>471.781</v>
       </c>
-      <c r="P19">
+      <c r="P19" t="n">
         <v>530.61</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" t="n">
         <v>557.0716</v>
       </c>
-      <c r="R19">
+      <c r="R19" t="n">
         <v>631.6772</v>
       </c>
-      <c r="S19">
+      <c r="S19" t="n">
         <v>717.5289</v>
       </c>
-      <c r="T19">
+      <c r="T19" t="n">
         <v>792.1146</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20">
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>1156.0674</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>1212.1674</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>1547.11</v>
       </c>
-      <c r="F20">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
         <v>2341.54</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>2615.6515</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>2967.0236</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>3355.2805</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>3495.8025</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>3429.5319</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>3540.7104</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>4431.4031</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="n">
         <v>4882.5093</v>
       </c>
-      <c r="O20">
+      <c r="O20" t="n">
         <v>5355.4466</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="n">
         <v>5962.7871</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" t="n">
         <v>6495.4441</v>
       </c>
-      <c r="R20">
+      <c r="R20" t="n">
         <v>7391.221</v>
       </c>
-      <c r="S20">
+      <c r="S20" t="n">
         <v>8288.8464</v>
       </c>
-      <c r="T20">
+      <c r="T20" t="n">
         <v>9095.9733</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21">
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>2473.69</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>2578.78</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>3420.65</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>4286.9189</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>4990.9744</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>5519.1683</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>6022.0823</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>6339.7531</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>6694.5512</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>7507.0901</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>8313.1325</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="n">
         <v>8502.959999999999</v>
       </c>
-      <c r="N21">
+      <c r="N21" t="n">
         <v>9981.2364</v>
       </c>
-      <c r="O21">
+      <c r="O21" t="n">
         <v>11677.3374</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="n">
         <v>14193.6258</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" t="n">
         <v>15623.01</v>
       </c>
-      <c r="R21">
+      <c r="R21" t="n">
         <v>19598.7629</v>
       </c>
-      <c r="S21">
+      <c r="S21" t="n">
         <v>23199.3852</v>
       </c>
-      <c r="T21">
+      <c r="T21" t="n">
         <v>25545.5428</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22">
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>1887.7333</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>1949.0667</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>2428.02</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>3010.1111</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>3590.5589</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>4036.2313</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>4622.963</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>5117.43</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>5352.1348</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>6059.03</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>6464.8837</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>6879.7137</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="n">
         <v>7728.5037</v>
       </c>
-      <c r="O22">
+      <c r="O22" t="n">
         <v>8992.959999999999</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="n">
         <v>10213.24</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" t="n">
         <v>11498.18</v>
       </c>
-      <c r="R22">
+      <c r="R22" t="n">
         <v>13923.74</v>
       </c>
-      <c r="S22">
+      <c r="S22" t="n">
         <v>16208.0792</v>
       </c>
-      <c r="T22">
+      <c r="T22" t="n">
         <v>18248.5802</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23">
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>1921.9758</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>1967.8306</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>2471.7753</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>2948.5416</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>3338.231</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>3729.4713</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>4318.8378</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>4765.4786</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>5147.6332</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>5769.2954</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>6145.5466</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>6495.2539</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="n">
         <v>7288.1388</v>
       </c>
-      <c r="O23">
+      <c r="O23" t="n">
         <v>8337.606100000001</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="n">
         <v>10329.8551</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" t="n">
         <v>11057.2697</v>
       </c>
-      <c r="R23">
+      <c r="R23" t="n">
         <v>12473.9706</v>
       </c>
-      <c r="S23">
+      <c r="S23" t="n">
         <v>13894.7362</v>
       </c>
-      <c r="T23">
+      <c r="T23" t="n">
         <v>15132.0048</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24">
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>1182.5655</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>1266.659</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>1588.528</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>1911.534</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>2187.6758</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>2427.4843</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>2888.739</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>3267.78</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>3541.3602</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>3951.4181</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>4279.9453</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>4465.7303</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="n">
         <v>5008.0833</v>
       </c>
-      <c r="O24">
+      <c r="O24" t="n">
         <v>6438.0943</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="n">
         <v>7584.1225</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" t="n">
         <v>8558.428900000001</v>
       </c>
-      <c r="R24">
+      <c r="R24" t="n">
         <v>10226.2713</v>
       </c>
-      <c r="S24">
+      <c r="S24" t="n">
         <v>11806.3832</v>
       </c>
-      <c r="T24">
+      <c r="T24" t="n">
         <v>13283.8734</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25">
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>海口</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>406.9576</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>430.9529</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>528.4629</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>610.29</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>772.03</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>852.1037</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>952.1479</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>1062.0955</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>1119.4789</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>1262.0625</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>1445.4862</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>3790.0965</v>
       </c>
-      <c r="N25">
+      <c r="N25" t="n">
         <v>1706.5</v>
       </c>
-      <c r="O25">
+      <c r="O25" t="n">
         <v>1838.6884</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="n">
         <v>2034.6349</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" t="n">
         <v>2222.012</v>
       </c>
-      <c r="R25">
+      <c r="R25" t="n">
         <v>2544.8224</v>
       </c>
-      <c r="S25">
+      <c r="S25" t="n">
         <v>2875.298</v>
       </c>
-      <c r="T25">
+      <c r="T25" t="n">
         <v>3154.8369</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26">
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>3744.7</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>3792.59</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>4905.93</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>5723.76</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>6717.05</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>7427.64</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>8389.059999999999</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>9289.370000000001</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>9974.01</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>9680.24</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>10391.14</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>10837.59</v>
       </c>
-      <c r="N26">
+      <c r="N26" t="n">
         <v>13478.94</v>
       </c>
-      <c r="O26">
+      <c r="O26" t="n">
         <v>16010.77</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="n">
         <v>18674.43</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" t="n">
         <v>20532.31</v>
       </c>
-      <c r="R26">
+      <c r="R26" t="n">
         <v>24610.06</v>
       </c>
-      <c r="S26">
+      <c r="S26" t="n">
         <v>27342.4</v>
       </c>
-      <c r="T26">
+      <c r="T26" t="n">
         <v>30759.0629</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27">
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>1553.2427</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>1694.7183</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>2180.1686</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>2567.4597</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>2920.3989</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>3243.5792</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>3735.4986</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>4157.597</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>4387.6724</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>4868.9313</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>5348.2</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>5641.6176</v>
       </c>
-      <c r="N27">
+      <c r="N27" t="n">
         <v>6473.2492</v>
       </c>
-      <c r="O27">
+      <c r="O27" t="n">
         <v>7630.0235</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="n">
         <v>8774.5821</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" t="n">
         <v>9858.0445</v>
       </c>
-      <c r="R27">
+      <c r="R27" t="n">
         <v>11671.0564</v>
       </c>
-      <c r="S27">
+      <c r="S27" t="n">
         <v>13553.9678</v>
       </c>
-      <c r="T27">
+      <c r="T27" t="n">
         <v>14831.0448</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28">
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>1311.3823</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>1375.3667</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>1709.8954</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>2048.2724</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>2329.0905</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>2550.7706</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>2939.4605</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>3296.6518</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>3483.7219</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>3685.2348</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>4087.5352</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>4385.2958</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="n">
         <v>5053.2878</v>
       </c>
-      <c r="O28">
+      <c r="O28" t="n">
         <v>6027.1085</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="n">
         <v>6951.5398</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" t="n">
         <v>7493.0416</v>
       </c>
-      <c r="R28">
+      <c r="R28" t="n">
         <v>9029.0756</v>
       </c>
-      <c r="S28">
+      <c r="S28" t="n">
         <v>10414.6443</v>
       </c>
-      <c r="T28">
+      <c r="T28" t="n">
         <v>11461.162</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29">
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>272.7921</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>297.0909</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>395.6199</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>480.2171</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>576.1104</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>680.0622</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>823.1473999999999</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>972.5048</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>1093.0883</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>1160.3297</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>1267.1813</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="n">
         <v>1339.1882</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="n">
         <v>1436.7707</v>
       </c>
-      <c r="O29">
+      <c r="O29" t="n">
         <v>1548.9274</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="n">
         <v>1723.8793</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" t="n">
         <v>1895.2041</v>
       </c>
-      <c r="R29">
+      <c r="R29" t="n">
         <v>2204.2747</v>
       </c>
-      <c r="S29">
+      <c r="S29" t="n">
         <v>2512.7646</v>
       </c>
-      <c r="T29">
+      <c r="T29" t="n">
         <v>2774.2893</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30">
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>1950.5281</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>1997.56</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>2504.41</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>3084.2</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>3677.77</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>4155.65</v>
       </c>
-      <c r="H30">
+      <c r="H30" t="n">
         <v>4787.03</v>
       </c>
-      <c r="I30">
+      <c r="I30" t="n">
         <v>5357.0459</v>
       </c>
-      <c r="J30">
+      <c r="J30" t="n">
         <v>5687.4866</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="n">
         <v>6571.1826</v>
       </c>
-      <c r="L30">
+      <c r="L30" t="n">
         <v>7035.81</v>
       </c>
-      <c r="M30">
+      <c r="M30" t="n">
         <v>7497.2963</v>
       </c>
-      <c r="N30">
+      <c r="N30" t="n">
         <v>8360.329</v>
       </c>
-      <c r="O30">
+      <c r="O30" t="n">
         <v>9553.929</v>
       </c>
-      <c r="P30">
+      <c r="P30" t="n">
         <v>10913.0545</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" t="n">
         <v>11996.543</v>
       </c>
-      <c r="R30">
+      <c r="R30" t="n">
         <v>14505.3767</v>
       </c>
-      <c r="S30">
+      <c r="S30" t="n">
         <v>16568.7083</v>
       </c>
-      <c r="T30">
+      <c r="T30" t="n">
         <v>18529.9052</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31">
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>582.2003999999999</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>614.1526</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>767.0527</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>921.9442</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>1088.7001</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>1251.0372</v>
       </c>
-      <c r="H31">
+      <c r="H31" t="n">
         <v>1498.2022</v>
       </c>
-      <c r="I31">
+      <c r="I31" t="n">
         <v>1827.1371</v>
       </c>
-      <c r="J31">
+      <c r="J31" t="n">
         <v>2010.5843</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="n">
         <v>2250.6008</v>
       </c>
-      <c r="L31">
+      <c r="L31" t="n">
         <v>2229.76</v>
       </c>
-      <c r="M31">
+      <c r="M31" t="n">
         <v>2646.0865</v>
       </c>
-      <c r="N31">
+      <c r="N31" t="n">
         <v>2835.739</v>
       </c>
-      <c r="O31">
+      <c r="O31" t="n">
         <v>3164.123</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="n">
         <v>3634.5806</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" t="n">
         <v>4008.7621</v>
       </c>
-      <c r="R31">
+      <c r="R31" t="n">
         <v>4646.4826</v>
       </c>
-      <c r="S31">
+      <c r="S31" t="n">
         <v>5195.819</v>
       </c>
-      <c r="T31">
+      <c r="T31" t="n">
         <v>5664.6213544937</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32">
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>1620.7242</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>1658.7095</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>2067.2209</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>2511.1685</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>2911.0048</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>3252.145</v>
       </c>
-      <c r="H32">
+      <c r="H32" t="n">
         <v>3845.4564</v>
       </c>
-      <c r="I32">
+      <c r="I32" t="n">
         <v>4475.3233</v>
       </c>
-      <c r="J32">
+      <c r="J32" t="n">
         <v>4839.2619</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="n">
         <v>5695.4874</v>
       </c>
-      <c r="L32">
+      <c r="L32" t="n">
         <v>6297.6278</v>
       </c>
-      <c r="M32">
+      <c r="M32" t="n">
         <v>6538.2301</v>
       </c>
-      <c r="N32">
+      <c r="N32" t="n">
         <v>7157.3151</v>
       </c>
-      <c r="O32">
+      <c r="O32" t="n">
         <v>7957.0399</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="n">
         <v>8961.7757</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" t="n">
         <v>9829.9429</v>
       </c>
-      <c r="R32">
+      <c r="R32" t="n">
         <v>11393.4867</v>
       </c>
-      <c r="S32">
+      <c r="S32" t="n">
         <v>12886.0729</v>
       </c>
-      <c r="T32">
+      <c r="T32" t="n">
         <v>14353.2313</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33">
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>2949.05</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>3228.19</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>3988.96</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>4908.7</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>5839.6576275277</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>6990.2463550016</v>
       </c>
-      <c r="H33">
+      <c r="H33" t="n">
         <v>8361.6</v>
       </c>
-      <c r="I33">
+      <c r="I33" t="n">
         <v>9622.3098592063</v>
       </c>
-      <c r="J33">
+      <c r="J33" t="n">
         <v>10774.1</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="n">
         <v>12207.2838</v>
       </c>
-      <c r="L33">
+      <c r="L33" t="n">
         <v>13399.4384</v>
       </c>
-      <c r="M33">
+      <c r="M33" t="n">
         <v>14367.3801</v>
       </c>
-      <c r="N33">
+      <c r="N33" t="n">
         <v>15907.2272</v>
       </c>
-      <c r="O33">
+      <c r="O33" t="n">
         <v>17860.3966</v>
       </c>
-      <c r="P33">
+      <c r="P33" t="n">
         <v>20209.8</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" t="n">
         <v>22239.893</v>
       </c>
-      <c r="R33">
+      <c r="R33" t="n">
         <v>25459</v>
       </c>
-      <c r="S33">
+      <c r="S33" t="n">
         <v>28899</v>
       </c>
-      <c r="T33">
+      <c r="T33" t="n">
         <v>31881.9407</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34">
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>306.3847</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>326.4143</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>423.1523</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>519.4029</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>634.4542</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>725.2604</v>
       </c>
-      <c r="H34">
+      <c r="H34" t="n">
         <v>901.4684999999999</v>
       </c>
-      <c r="I34">
+      <c r="I34" t="n">
         <v>1015.222</v>
       </c>
-      <c r="J34">
+      <c r="J34" t="n">
         <v>1089.8949</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="n">
         <v>1304.971</v>
       </c>
-      <c r="L34">
+      <c r="L34" t="n">
         <v>1391.3467</v>
       </c>
-      <c r="M34">
+      <c r="M34" t="n">
         <v>1496.9408</v>
       </c>
-      <c r="N34">
+      <c r="N34" t="n">
         <v>1664.8</v>
       </c>
-      <c r="O34">
+      <c r="O34" t="n">
         <v>1867.0136</v>
       </c>
-      <c r="P34">
+      <c r="P34" t="n">
         <v>2137.4756</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" t="n">
         <v>2323.502</v>
       </c>
-      <c r="R34">
+      <c r="R34" t="n">
         <v>2693.8748</v>
       </c>
-      <c r="S34">
+      <c r="S34" t="n">
         <v>3114.7299</v>
       </c>
-      <c r="T34">
+      <c r="T34" t="n">
         <v>3452.7456</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35">
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>1174.5969</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>1202.0796</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>1507.3851</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>1834.1564</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>2062.7232</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>2337.7846</v>
       </c>
-      <c r="H35">
+      <c r="H35" t="n">
         <v>2767.3822</v>
       </c>
-      <c r="I35">
+      <c r="I35" t="n">
         <v>3107.1578</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="n">
         <v>3380.1096</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="n">
         <v>3792.78</v>
       </c>
-      <c r="L35">
+      <c r="L35" t="n">
         <v>4218.0932</v>
       </c>
-      <c r="M35">
+      <c r="M35" t="n">
         <v>4566.9938</v>
       </c>
-      <c r="N35">
+      <c r="N35" t="n">
         <v>4993.2387</v>
       </c>
-      <c r="O35">
+      <c r="O35" t="n">
         <v>5889.0932</v>
       </c>
-      <c r="P35">
+      <c r="P35" t="n">
         <v>6896.3</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" t="n">
         <v>8257.525600000001</v>
       </c>
-      <c r="R35">
+      <c r="R35" t="n">
         <v>9465.2773</v>
       </c>
-      <c r="S35">
+      <c r="S35" t="n">
         <v>10750.1428</v>
       </c>
-      <c r="T35">
+      <c r="T35" t="n">
         <v>11746.7608</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36">
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>1093.04</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>1177.17</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>1494.9281</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>1881.3226</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>2172.0771</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>2526.9331</v>
       </c>
-      <c r="H36">
+      <c r="H36" t="n">
         <v>2981.31</v>
       </c>
-      <c r="I36">
+      <c r="I36" t="n">
         <v>3482.97</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="n">
         <v>3866.7891</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="n">
         <v>4348.5503</v>
       </c>
-      <c r="L36">
+      <c r="L36" t="n">
         <v>4868.6355</v>
       </c>
-      <c r="M36">
+      <c r="M36" t="n">
         <v>5200.2123</v>
       </c>
-      <c r="N36">
+      <c r="N36" t="n">
         <v>5692.0847</v>
       </c>
-      <c r="O36">
+      <c r="O36" t="n">
         <v>6530.5194</v>
       </c>
-      <c r="P36">
+      <c r="P36" t="n">
         <v>7501.6412</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" t="n">
         <v>8245.940000000001</v>
       </c>
-      <c r="R36">
+      <c r="R36" t="n">
         <v>9703.392900000001</v>
       </c>
-      <c r="S36">
+      <c r="S36" t="n">
         <v>11132.3522</v>
       </c>
-      <c r="T36">
+      <c r="T36" t="n">
         <v>12423.8513</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37">
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>1567.6197</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>1702.0383</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>2123.3637</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>2527.8658</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>2912.3256</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>3198.5099</v>
       </c>
-      <c r="H37">
+      <c r="H37" t="n">
         <v>3757.6007</v>
       </c>
-      <c r="I37">
+      <c r="I37" t="n">
         <v>4140.5946</v>
       </c>
-      <c r="J37">
+      <c r="J37" t="n">
         <v>4435.8964</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="n">
         <v>5023.5905</v>
       </c>
-      <c r="L37">
+      <c r="L37" t="n">
         <v>5326.3262</v>
       </c>
-      <c r="M37">
+      <c r="M37" t="n">
         <v>5394.1843</v>
       </c>
-      <c r="N37">
+      <c r="N37" t="n">
         <v>5913.7089</v>
       </c>
-      <c r="O37">
+      <c r="O37" t="n">
         <v>6755.237</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="n">
         <v>8030.9469</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" t="n">
         <v>9028.235199999999</v>
       </c>
-      <c r="R37">
+      <c r="R37" t="n">
         <v>10948.2351</v>
       </c>
-      <c r="S37">
+      <c r="S37" t="n">
         <v>12758.5665</v>
       </c>
-      <c r="T37">
+      <c r="T37" t="n">
         <v>14168.1378</v>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_raw/individual_deposit.xlsx
+++ b/data_raw/individual_deposit.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,11 +529,6 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -598,7 +593,6 @@
       <c r="T2" t="n">
         <v>63910.9863</v>
       </c>
-      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -663,7 +657,6 @@
       <c r="T3" t="n">
         <v>5905.76</v>
       </c>
-      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -728,7 +721,6 @@
       <c r="T4" t="n">
         <v>5639.5427</v>
       </c>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -793,7 +785,6 @@
       <c r="T5" t="n">
         <v>70398.14599999999</v>
       </c>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -858,7 +849,6 @@
       <c r="T6" t="n">
         <v>17091.8481</v>
       </c>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -923,7 +913,6 @@
       <c r="T7" t="n">
         <v>6713.2205</v>
       </c>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -988,7 +977,6 @@
       <c r="T8" t="n">
         <v>7516.1403</v>
       </c>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1053,7 +1041,6 @@
       <c r="T9" t="n">
         <v>6546.1784</v>
       </c>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1118,7 +1105,6 @@
       <c r="T10" t="n">
         <v>10785.8387</v>
       </c>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1183,7 +1169,6 @@
       <c r="T11" t="n">
         <v>3771.4489</v>
       </c>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1248,7 +1233,6 @@
       <c r="T12" t="n">
         <v>12056.2573</v>
       </c>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1313,7 +1297,6 @@
       <c r="T13" t="n">
         <v>12401.4925</v>
       </c>
-      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1378,7 +1361,6 @@
       <c r="T14" t="n">
         <v>24069.6285</v>
       </c>
-      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1443,7 +1425,6 @@
       <c r="T15" t="n">
         <v>9741.197399999999</v>
       </c>
-      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1508,7 +1489,6 @@
       <c r="T16" t="n">
         <v>16255.5179</v>
       </c>
-      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1573,7 +1553,6 @@
       <c r="T17" t="n">
         <v>32394.0385</v>
       </c>
-      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1638,7 +1617,6 @@
       <c r="T18" t="n">
         <v>28991.8879</v>
       </c>
-      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1695,7 +1673,6 @@
       <c r="T19" t="n">
         <v>792.1146</v>
       </c>
-      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1758,7 +1735,6 @@
       <c r="T20" t="n">
         <v>9095.9733</v>
       </c>
-      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1823,7 +1799,6 @@
       <c r="T21" t="n">
         <v>25545.5428</v>
       </c>
-      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1888,7 +1863,6 @@
       <c r="T22" t="n">
         <v>18248.5802</v>
       </c>
-      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1953,7 +1927,6 @@
       <c r="T23" t="n">
         <v>15132.0048</v>
       </c>
-      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2018,7 +1991,6 @@
       <c r="T24" t="n">
         <v>13283.8734</v>
       </c>
-      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2083,7 +2055,6 @@
       <c r="T25" t="n">
         <v>3154.8369</v>
       </c>
-      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2148,7 +2119,6 @@
       <c r="T26" t="n">
         <v>30759.0629</v>
       </c>
-      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2213,7 +2183,6 @@
       <c r="T27" t="n">
         <v>14831.0448</v>
       </c>
-      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2278,7 +2247,6 @@
       <c r="T28" t="n">
         <v>11461.162</v>
       </c>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2343,7 +2311,6 @@
       <c r="T29" t="n">
         <v>2774.2893</v>
       </c>
-      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2408,7 +2375,6 @@
       <c r="T30" t="n">
         <v>18529.9052</v>
       </c>
-      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2473,7 +2439,6 @@
       <c r="T31" t="n">
         <v>5664.6213544937</v>
       </c>
-      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2538,7 +2503,6 @@
       <c r="T32" t="n">
         <v>14353.2313</v>
       </c>
-      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -2603,7 +2567,6 @@
       <c r="T33" t="n">
         <v>31881.9407</v>
       </c>
-      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -2668,7 +2631,6 @@
       <c r="T34" t="n">
         <v>3452.7456</v>
       </c>
-      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -2733,7 +2695,6 @@
       <c r="T35" t="n">
         <v>11746.7608</v>
       </c>
-      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -2798,7 +2759,6 @@
       <c r="T36" t="n">
         <v>12423.8513</v>
       </c>
-      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -2863,7 +2823,6 @@
       <c r="T37" t="n">
         <v>14168.1378</v>
       </c>
-      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
